--- a/api/templates/result_notifications/en.xlsx
+++ b/api/templates/result_notifications/en.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C593FB49-9594-DE40-B005-895ADEE7AC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="SMS" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Email" state="visible" r:id="rId5"/>
+    <sheet name="SMS" sheetId="1" r:id="rId1"/>
+    <sheet name="Email" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -125,49 +126,49 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -193,17 +194,33 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -213,13 +230,13 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -228,16 +245,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -256,62 +273,377 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.30078125"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
     <col min="2" max="2" width="27.5" customWidth="1"/>
-    <col min="3" max="3" width="19.3" customWidth="1"/>
-    <col min="4" max="4" width="15.3" customWidth="1"/>
-    <col min="5" max="5" width="15.2" customWidth="1"/>
-    <col min="6" max="6" width="43.09" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="16.4" customWidth="1"/>
-    <col min="9" max="9" width="17.6" customWidth="1"/>
-    <col min="10" max="10" width="15.2" customWidth="1"/>
-    <col min="11" max="11" width="53.2" customWidth="1"/>
-    <col min="16384" max="16384" width="9.34" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="36.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" customWidth="1"/>
+    <col min="11" max="11" width="53.1640625" customWidth="1"/>
+    <col min="16384" max="16384" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="17.9" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -346,7 +678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -381,41 +713,40 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.30078125"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
     <col min="2" max="2" width="27.5" customWidth="1"/>
-    <col min="3" max="4" width="30.1" customWidth="1"/>
-    <col min="5" max="5" width="33.8" customWidth="1"/>
-    <col min="6" max="6" width="15.2" customWidth="1"/>
-    <col min="7" max="7" width="53.1" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="16.4" customWidth="1"/>
-    <col min="10" max="10" width="17.6" customWidth="1"/>
-    <col min="11" max="11" width="15.2" customWidth="1"/>
-    <col min="12" max="12" width="53.2" customWidth="1"/>
-    <col min="16384" max="16384" width="9.34" customWidth="1"/>
+    <col min="3" max="4" width="30.1640625" customWidth="1"/>
+    <col min="5" max="5" width="33.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="36.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" customWidth="1"/>
+    <col min="12" max="12" width="53.1640625" customWidth="1"/>
+    <col min="16384" max="16384" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -423,37 +754,37 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="17.9" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -491,7 +822,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -529,11 +860,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="8:12" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F11" s="8"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -541,6 +871,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>